--- a/exports/KAYNES_full_report.xlsx
+++ b/exports/KAYNES_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:U63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>16.2</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44914.38541666666</v>
+        <v>44914.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>697.9</v>
+        <v>693.5</v>
       </c>
       <c r="I2" t="n">
         <v>693.7182562532929</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-5.94</v>
+        <v>-6.53</v>
       </c>
       <c r="L2" t="n">
-        <v>6.19</v>
+        <v>6.84</v>
       </c>
       <c r="M2" t="n">
         <v>1.33</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>6.34</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44923.55208333334</v>
+        <v>44924.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>734.7</v>
+        <v>745.15</v>
       </c>
       <c r="I3" t="n">
         <v>737.221589185419</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.94</v>
+        <v>-7.45</v>
       </c>
       <c r="L3" t="n">
-        <v>7.46</v>
+        <v>8.93</v>
       </c>
       <c r="M3" t="n">
         <v>0.48</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S3" t="b">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.4</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44985.38541666666</v>
+        <v>44985.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>877.85</v>
+        <v>862</v>
       </c>
       <c r="I4" t="n">
         <v>867.8712809219095</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>17.81</v>
+        <v>15.68</v>
       </c>
       <c r="L4" t="n">
         <v>2.75</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>10.31</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44995.38541666666</v>
+        <v>44995.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>934</v>
+        <v>968</v>
       </c>
       <c r="I5" t="n">
         <v>950.8453244455794</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.35</v>
+        <v>-12.3</v>
       </c>
       <c r="L5" t="n">
-        <v>11.32</v>
+        <v>12.34</v>
       </c>
       <c r="M5" t="n">
         <v>1.02</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>10</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>965.75</v>
+        <v>947.05</v>
       </c>
       <c r="I6" t="n">
         <v>952.5050750149535</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>27</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.23</v>
+        <v>-2.16</v>
       </c>
       <c r="L6" t="n">
         <v>4.78</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>10.6</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>45044.55208333334</v>
+        <v>45048.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>981.1</v>
+        <v>1002.5</v>
       </c>
       <c r="I7" t="n">
         <v>1001.15774554434</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.6</v>
+        <v>-5.86</v>
       </c>
       <c r="L7" t="n">
-        <v>5.01</v>
+        <v>7.04</v>
       </c>
       <c r="M7" t="n">
-        <v>0.97</v>
+        <v>1.33</v>
       </c>
       <c r="N7" t="n">
         <v>3.3</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>5.13</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>45148.38541666666</v>
+        <v>45148.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1750</v>
+        <v>1722</v>
       </c>
       <c r="I8" t="n">
         <v>1723.13619936394</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>100</v>
+        <v>100.1666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>74.56</v>
+        <v>71.77</v>
       </c>
       <c r="L8" t="n">
         <v>5.03</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>143</v>
+        <v>144</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>7.89</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>45161.55208333334</v>
+        <v>45162.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1799</v>
+        <v>1861.8</v>
       </c>
       <c r="I9" t="n">
         <v>1857.919689334335</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.47</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>7.91</v>
+        <v>9.68</v>
       </c>
       <c r="M9" t="n">
         <v>1.25</v>
       </c>
       <c r="N9" t="n">
-        <v>1.77</v>
+        <v>3.11</v>
       </c>
       <c r="O9" t="n">
         <v>-3.64</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.81</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>45219.38541666666</v>
+        <v>45219.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>2531.3</v>
+        <v>2449.65</v>
       </c>
       <c r="I10" t="n">
         <v>2457.910819199716</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>57</v>
+        <v>57.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>35.96</v>
+        <v>31.57</v>
       </c>
       <c r="L10" t="n">
         <v>3.59</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.23</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>45240.55208333334</v>
+        <v>45242.76041666666</v>
       </c>
       <c r="H11" t="n">
-        <v>2451</v>
+        <v>2540</v>
       </c>
       <c r="I11" t="n">
         <v>2514.244256067464</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>21</v>
+        <v>23.20833333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06</v>
+        <v>-3.69</v>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="M11" t="n">
         <v>2.21</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>45267.55208333334</v>
+        <v>45268.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>2377</v>
+        <v>2298.75</v>
       </c>
       <c r="I12" t="n">
         <v>2342.983294635871</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>24.79166666666667</v>
+        <v>25.625</v>
       </c>
       <c r="K12" t="n">
-        <v>-6.42</v>
+        <v>-9.5</v>
       </c>
       <c r="L12" t="n">
-        <v>7.05</v>
+        <v>10.4</v>
       </c>
       <c r="M12" t="n">
         <v>1.08</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>7.73</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>45274.55208333334</v>
+        <v>45275.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>2472.6</v>
+        <v>2580</v>
       </c>
       <c r="I13" t="n">
         <v>2476.461996020416</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.56</v>
+        <v>-12.23</v>
       </c>
       <c r="L13" t="n">
-        <v>8.75</v>
+        <v>15.06</v>
       </c>
       <c r="M13" t="n">
         <v>1.67</v>
       </c>
       <c r="N13" t="n">
-        <v>2.81</v>
+        <v>4.34</v>
       </c>
       <c r="O13" t="n">
         <v>-0.36</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>7.7</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>45282.55208333334</v>
+        <v>45286.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>2749.9</v>
+        <v>2611</v>
       </c>
       <c r="I14" t="n">
         <v>2633.799414393935</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>11</v>
       </c>
       <c r="K14" t="n">
-        <v>6.59</v>
+        <v>1.2</v>
       </c>
       <c r="L14" t="n">
         <v>4.1</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.9</v>
+        <v>4.43</v>
       </c>
       <c r="O14" t="n">
         <v>4.34</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>15.42</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45303.55208333334</v>
+        <v>45306.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>2725</v>
+        <v>2789.25</v>
       </c>
       <c r="I15" t="n">
         <v>2765.363159902887</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.37</v>
+        <v>-6.83</v>
       </c>
       <c r="L15" t="n">
-        <v>5.04</v>
+        <v>8.52</v>
       </c>
       <c r="M15" t="n">
         <v>1.67</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>7</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>3003.05</v>
+        <v>2806</v>
       </c>
       <c r="I16" t="n">
         <v>2900.778349509199</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K16" t="n">
-        <v>7.67</v>
+        <v>0.6</v>
       </c>
       <c r="L16" t="n">
         <v>8.380000000000001</v>
@@ -1353,7 +1544,7 @@
         <v>1.48</v>
       </c>
       <c r="N16" t="n">
-        <v>4.98</v>
+        <v>6.26</v>
       </c>
       <c r="O16" t="n">
         <v>1.47</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>16.91</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45408.38541666666</v>
+        <v>45408.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>2658.2</v>
+        <v>2715</v>
       </c>
       <c r="I17" t="n">
         <v>2670.848566078438</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>45</v>
+        <v>45.16666666666666</v>
       </c>
       <c r="K17" t="n">
-        <v>5.27</v>
+        <v>3.24</v>
       </c>
       <c r="L17" t="n">
         <v>8.02</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>7.94</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45415.55208333334</v>
+        <v>45418.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2542.2</v>
+        <v>2508</v>
       </c>
       <c r="I18" t="n">
         <v>2528.076847041737</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K18" t="n">
-        <v>-6.36</v>
+        <v>-7.62</v>
       </c>
       <c r="L18" t="n">
-        <v>7.31</v>
+        <v>8.84</v>
       </c>
       <c r="M18" t="n">
         <v>0.11</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>8.76</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2586.95</v>
+        <v>3027.8</v>
       </c>
       <c r="I19" t="n">
         <v>2638.135165823684</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.15</v>
+        <v>-20.73</v>
       </c>
       <c r="L19" t="n">
-        <v>5.82</v>
+        <v>22.84</v>
       </c>
       <c r="M19" t="n">
-        <v>0.98</v>
+        <v>14.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.43</v>
+        <v>19.09</v>
       </c>
       <c r="O19" t="n">
         <v>-1.66</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>13.07</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>3529</v>
+        <v>2814</v>
       </c>
       <c r="I20" t="n">
         <v>3164.648508528565</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K20" t="n">
-        <v>16.55</v>
+        <v>-7.06</v>
       </c>
       <c r="L20" t="n">
-        <v>6.98</v>
+        <v>7.06</v>
       </c>
       <c r="M20" t="n">
         <v>0.93</v>
       </c>
       <c r="N20" t="n">
-        <v>3.04</v>
+        <v>20.26</v>
       </c>
       <c r="O20" t="n">
         <v>19.09</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>31.28</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45453.55208333334</v>
+        <v>45454.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>3376.1</v>
+        <v>3584.9</v>
       </c>
       <c r="I21" t="n">
         <v>3469.379313554408</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-19.98</v>
+        <v>-27.4</v>
       </c>
       <c r="L21" t="n">
-        <v>25.41</v>
+        <v>28.36</v>
       </c>
       <c r="M21" t="n">
         <v>3.78</v>
       </c>
       <c r="N21" t="n">
-        <v>6.45</v>
+        <v>7.66</v>
       </c>
       <c r="O21" t="n">
         <v>-20.26</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>17.26</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45492.38541666666</v>
+        <v>45492.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>3962.95</v>
+        <v>3888.75</v>
       </c>
       <c r="I22" t="n">
         <v>3949.94737959874</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>38</v>
+        <v>38.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>10.55</v>
+        <v>8.48</v>
       </c>
       <c r="L22" t="n">
         <v>5.23</v>
@@ -1704,7 +1967,19 @@
         <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>10.4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45499.55208333334</v>
+        <v>45502.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>4237</v>
+        <v>4601.9</v>
       </c>
       <c r="I23" t="n">
         <v>4293.229955142667</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K23" t="n">
-        <v>-8.960000000000001</v>
+        <v>-18.34</v>
       </c>
       <c r="L23" t="n">
-        <v>10.04</v>
+        <v>21.61</v>
       </c>
       <c r="M23" t="n">
-        <v>0.73</v>
+        <v>6.09</v>
       </c>
       <c r="N23" t="n">
-        <v>2.41</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>-4.59</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>11.8</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>4353</v>
+        <v>4130.55</v>
       </c>
       <c r="I24" t="n">
         <v>4142.534972757972</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K24" t="n">
-        <v>-5.41</v>
+        <v>-10.24</v>
       </c>
       <c r="L24" t="n">
-        <v>8.18</v>
+        <v>11.67</v>
       </c>
       <c r="M24" t="n">
-        <v>1.35</v>
+        <v>3.51</v>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>2.87</v>
       </c>
       <c r="O24" t="n">
         <v>8.449999999999999</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>11.23</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45516.55208333334</v>
+        <v>45517.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>4297</v>
+        <v>4664.5</v>
       </c>
       <c r="I25" t="n">
         <v>4583.231975685719</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.03</v>
+        <v>-12.93</v>
       </c>
       <c r="L25" t="n">
-        <v>5.67</v>
+        <v>13.71</v>
       </c>
       <c r="M25" t="n">
         <v>2.89</v>
       </c>
       <c r="N25" t="n">
-        <v>2.63</v>
+        <v>8.68</v>
       </c>
       <c r="O25" t="n">
         <v>-2.87</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>12.01</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>4763</v>
+        <v>4669.8</v>
       </c>
       <c r="I26" t="n">
         <v>4692.319376868551</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K26" t="n">
-        <v>2.11</v>
+        <v>0.11</v>
       </c>
       <c r="L26" t="n">
         <v>7.84</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>10.32</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45546.55208333334</v>
+        <v>45547.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>4650</v>
+        <v>5246.85</v>
       </c>
       <c r="I27" t="n">
         <v>5020.064962526176</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
-        <v>0.42</v>
+        <v>-12.36</v>
       </c>
       <c r="L27" t="n">
-        <v>8.140000000000001</v>
+        <v>14.03</v>
       </c>
       <c r="M27" t="n">
         <v>3.98</v>
       </c>
       <c r="N27" t="n">
-        <v>4.82</v>
+        <v>10.54</v>
       </c>
       <c r="O27" t="n">
         <v>-2.9</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.19</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45568.55208333334</v>
+        <v>45569.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>5200.75</v>
+        <v>5068</v>
       </c>
       <c r="I28" t="n">
         <v>5159.917703048821</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.88</v>
+        <v>-3.41</v>
       </c>
       <c r="L28" t="n">
         <v>9.800000000000001</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>10.64</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45573.55208333334</v>
+        <v>45574.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>5250</v>
+        <v>5427</v>
       </c>
       <c r="I29" t="n">
         <v>5329.779359105111</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.59</v>
+        <v>-7.08</v>
       </c>
       <c r="L29" t="n">
-        <v>4.31</v>
+        <v>7.87</v>
       </c>
       <c r="M29" t="n">
         <v>0.51</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.33</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45593.55208333334</v>
+        <v>45594.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>5345</v>
+        <v>5201.85</v>
       </c>
       <c r="I30" t="n">
         <v>5257.697518228264</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.51</v>
+        <v>-4.15</v>
       </c>
       <c r="L30" t="n">
         <v>5</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>12.07</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H31" t="n">
-        <v>5697.55</v>
+        <v>5896</v>
       </c>
       <c r="I31" t="n">
         <v>5775.69450947658</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K31" t="n">
-        <v>-9.529999999999999</v>
+        <v>-13.34</v>
       </c>
       <c r="L31" t="n">
-        <v>10.25</v>
+        <v>14.13</v>
       </c>
       <c r="M31" t="n">
         <v>4.91</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>11.35</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>7249.95</v>
+        <v>6915</v>
       </c>
       <c r="I32" t="n">
         <v>6974.701172535906</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>62</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K32" t="n">
-        <v>22.96</v>
+        <v>17.28</v>
       </c>
       <c r="L32" t="n">
         <v>9.24</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>13.04</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45734.38541666666</v>
+        <v>45734.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>4468.05</v>
+        <v>4493</v>
       </c>
       <c r="I33" t="n">
         <v>4475.346453643145</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>69</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>35.39</v>
+        <v>35.03</v>
       </c>
       <c r="L33" t="n">
         <v>6.12</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,25 +2765,25 @@
         <v>10.63</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>4665</v>
+        <v>4232.4</v>
       </c>
       <c r="I34" t="n">
         <v>4581.653081384729</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>17</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>3.83</v>
+        <v>-5.8</v>
       </c>
       <c r="L34" t="n">
-        <v>0.95</v>
+        <v>13.2</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2</v>
+        <v>16.4</v>
       </c>
       <c r="N34" t="n">
         <v>5.76</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>13.5</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45755.38541666666</v>
+        <v>45755.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>4723.9</v>
+        <v>4825</v>
       </c>
       <c r="I35" t="n">
         <v>4803.63474410615</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1</v>
+        <v>1.166666666666667</v>
       </c>
       <c r="K35" t="n">
-        <v>-11.61</v>
+        <v>-14</v>
       </c>
       <c r="L35" t="n">
-        <v>12.19</v>
+        <v>15.13</v>
       </c>
       <c r="M35" t="n">
         <v>3.22</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>15.18</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45796.55208333334</v>
+        <v>45797.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>6099</v>
+        <v>5983</v>
       </c>
       <c r="I36" t="n">
         <v>5990.911759011505</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>41</v>
+        <v>41.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>26.4</v>
+        <v>24</v>
       </c>
       <c r="L36" t="n">
         <v>2.99</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>11.37</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45826.38541666666</v>
+        <v>45826.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>5674</v>
+        <v>5709</v>
       </c>
       <c r="I37" t="n">
         <v>5690.510257854224</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>5.16</v>
+        <v>4.58</v>
       </c>
       <c r="L37" t="n">
         <v>3.13</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>6.62</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>5955</v>
+        <v>5882</v>
       </c>
       <c r="I38" t="n">
         <v>5887.564336258168</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>4.31</v>
+        <v>3.03</v>
       </c>
       <c r="L38" t="n">
         <v>2.26</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>5.72</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>5640</v>
+        <v>6185</v>
       </c>
       <c r="I39" t="n">
         <v>5783.395455578493</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K39" t="n">
-        <v>4.11</v>
+        <v>-5.15</v>
       </c>
       <c r="L39" t="n">
-        <v>1.74</v>
+        <v>6.83</v>
       </c>
       <c r="M39" t="n">
         <v>0.67</v>
       </c>
       <c r="N39" t="n">
-        <v>1.67</v>
+        <v>9.93</v>
       </c>
       <c r="O39" t="n">
         <v>-1.75</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>13.94</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45877.38541666666</v>
+        <v>45877.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>5934</v>
+        <v>5800</v>
       </c>
       <c r="I40" t="n">
         <v>5905.734806045462</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.06</v>
+        <v>-6.22</v>
       </c>
       <c r="L40" t="n">
         <v>11.45</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,25 +3248,25 @@
         <v>10.01</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>6110</v>
+        <v>6312.5</v>
       </c>
       <c r="I41" t="n">
         <v>6232.720209294328</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>6</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.34</v>
+        <v>-8.84</v>
       </c>
       <c r="L41" t="n">
-        <v>6.46</v>
+        <v>9.31</v>
       </c>
       <c r="M41" t="n">
-        <v>0.45</v>
+        <v>2.26</v>
       </c>
       <c r="N41" t="n">
         <v>4.83</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>7.99</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45929.38541666666</v>
+        <v>45929.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>7123</v>
+        <v>7066</v>
       </c>
       <c r="I42" t="n">
         <v>7122.657334356636</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K42" t="n">
-        <v>12.84</v>
+        <v>11.94</v>
       </c>
       <c r="L42" t="n">
         <v>4.07</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>7</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45936.38541666666</v>
+        <v>45936.55208333334</v>
       </c>
       <c r="H43" t="n">
-        <v>7284</v>
+        <v>7529.5</v>
       </c>
       <c r="I43" t="n">
         <v>7477.635762822175</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>-3.09</v>
+        <v>-6.56</v>
       </c>
       <c r="L43" t="n">
-        <v>3.5</v>
+        <v>8.26</v>
       </c>
       <c r="M43" t="n">
         <v>0.76</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>7.31</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45938.55208333334</v>
+        <v>45939.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>7172</v>
+        <v>7118</v>
       </c>
       <c r="I44" t="n">
         <v>7141.158993379217</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K44" t="n">
-        <v>-4.75</v>
+        <v>-5.47</v>
       </c>
       <c r="L44" t="n">
-        <v>4.83</v>
+        <v>5.94</v>
       </c>
       <c r="M44" t="n">
         <v>0.33</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46052.55208333334</v>
+        <v>46054.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>3473</v>
+        <v>3590.4</v>
       </c>
       <c r="I45" t="n">
         <v>3590.236109854264</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>113.1666666666667</v>
+        <v>115</v>
       </c>
       <c r="K45" t="n">
-        <v>51.21</v>
+        <v>49.56</v>
       </c>
       <c r="L45" t="n">
         <v>2.16</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>153</v>
+        <v>154</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>5</v>
+      </c>
+      <c r="U45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>11.11</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46080.55208333334</v>
+        <v>46083.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3840</v>
+        <v>3692.2</v>
       </c>
       <c r="I46" t="n">
         <v>3694.546193420949</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K46" t="n">
-        <v>6.95</v>
+        <v>2.84</v>
       </c>
       <c r="L46" t="n">
         <v>7.05</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>10.42</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46118.55208333334</v>
+        <v>46119.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>3703</v>
+        <v>3767.1</v>
       </c>
       <c r="I47" t="n">
         <v>3716.038492972171</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.29</v>
+        <v>-2.03</v>
       </c>
       <c r="L47" t="n">
         <v>5.6</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>11.94</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46141.38541666666</v>
+        <v>46141.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>4191.2</v>
+        <v>4117.4</v>
       </c>
       <c r="I48" t="n">
         <v>4118.375662690829</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>22</v>
+        <v>22.16666666666667</v>
       </c>
       <c r="K48" t="n">
-        <v>11.26</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L48" t="n">
         <v>3.51</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.97</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46149.38541666666</v>
+        <v>46149.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>4329.5</v>
+        <v>4380</v>
       </c>
       <c r="I49" t="n">
         <v>4332.853274571471</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.15</v>
+        <v>-6.38</v>
       </c>
       <c r="L49" t="n">
         <v>6.62</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>7.03</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>4370</v>
+        <v>4140</v>
       </c>
       <c r="I50" t="n">
         <v>4205.561131490868</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.23</v>
+        <v>-5.48</v>
       </c>
       <c r="L50" t="n">
-        <v>1.47</v>
+        <v>5.84</v>
       </c>
       <c r="M50" t="n">
-        <v>0.46</v>
+        <v>0.64</v>
       </c>
       <c r="N50" t="n">
-        <v>2.82</v>
+        <v>6.91</v>
       </c>
       <c r="O50" t="n">
         <v>1.82</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>10.82</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46167.38541666666</v>
+        <v>46167.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>3380</v>
+        <v>3401</v>
       </c>
       <c r="I51" t="n">
         <v>3382.013834902549</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>18.36</v>
+        <v>17.85</v>
       </c>
       <c r="L51" t="n">
         <v>5.7</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>3124.9</v>
+        <v>3039</v>
       </c>
       <c r="I52" t="n">
         <v>3082.704333015554</v>
       </c>
       <c r="J52" s="2" t="n">
+        <v>13.83333333333333</v>
+      </c>
+      <c r="K52" t="n">
+        <v>-10.64</v>
+      </c>
+      <c r="L52" t="n">
         <v>11</v>
       </c>
-      <c r="K52" t="n">
-        <v>-8.119999999999999</v>
-      </c>
-      <c r="L52" t="n">
-        <v>9.67</v>
-      </c>
       <c r="M52" t="n">
-        <v>0.96</v>
+        <v>1.76</v>
       </c>
       <c r="N52" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="O52" t="n">
         <v>2.29</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>8.1</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46189.55208333334</v>
+        <v>46190.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>3176</v>
+        <v>3255.9</v>
       </c>
       <c r="I53" t="n">
         <v>3203.130563225935</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K53" t="n">
-        <v>-4.51</v>
+        <v>-7.14</v>
       </c>
       <c r="L53" t="n">
-        <v>6.28</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M53" t="n">
         <v>1.97</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.21</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46203.38541666666</v>
+        <v>46203.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>3161</v>
+        <v>3130</v>
       </c>
       <c r="I54" t="n">
         <v>3156.313104391152</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.91</v>
+        <v>-3.87</v>
       </c>
       <c r="L54" t="n">
-        <v>4.04</v>
+        <v>4.48</v>
       </c>
       <c r="M54" t="n">
         <v>0.07000000000000001</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>7.79</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46212.38541666666</v>
+        <v>46212.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>3349.8</v>
+        <v>3445.1</v>
       </c>
       <c r="I55" t="n">
         <v>3356.931906198019</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>-7.02</v>
+        <v>-10.07</v>
       </c>
       <c r="L55" t="n">
-        <v>8.56</v>
+        <v>10.54</v>
       </c>
       <c r="M55" t="n">
         <v>0.75</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46226.55208333334</v>
+        <v>46227.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>3240</v>
+        <v>3182.6</v>
       </c>
       <c r="I56" t="n">
         <v>3210.853053007006</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>-5.95</v>
+        <v>-7.62</v>
       </c>
       <c r="L56" t="n">
-        <v>6.97</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="M56" t="n">
         <v>1.17</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>6.13</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>3247</v>
+        <v>3662.7</v>
       </c>
       <c r="I57" t="n">
         <v>3360.658184496257</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>-2.02</v>
+        <v>-15.09</v>
       </c>
       <c r="L57" t="n">
-        <v>2.12</v>
+        <v>15.79</v>
       </c>
       <c r="M57" t="n">
         <v>1.13</v>
       </c>
       <c r="N57" t="n">
-        <v>2.07</v>
+        <v>12.57</v>
       </c>
       <c r="O57" t="n">
         <v>-2.01</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>12.84</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46251.38541666666</v>
+        <v>46251.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>3692.9</v>
+        <v>3654</v>
       </c>
       <c r="I58" t="n">
         <v>3656.062848564991</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>0.82</v>
+        <v>-0.24</v>
       </c>
       <c r="L58" t="n">
         <v>10.72</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>7.8</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46255.38541666666</v>
+        <v>46255.55208333334</v>
       </c>
       <c r="H59" t="n">
-        <v>3893</v>
+        <v>3902</v>
       </c>
       <c r="I59" t="n">
         <v>3899.65414995915</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3.833333333333333</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.54</v>
+        <v>-6.79</v>
       </c>
       <c r="L59" t="n">
-        <v>6.65</v>
+        <v>7.1</v>
       </c>
       <c r="M59" t="n">
         <v>0.3</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>6.38</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46262.55208333334</v>
+        <v>46265.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>3945</v>
+        <v>3756.5</v>
       </c>
       <c r="I60" t="n">
         <v>3796.697451236522</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K60" t="n">
-        <v>1.1</v>
+        <v>-3.73</v>
       </c>
       <c r="L60" t="n">
-        <v>2.51</v>
+        <v>4.35</v>
       </c>
       <c r="M60" t="n">
         <v>0.74</v>
       </c>
       <c r="N60" t="n">
-        <v>1.74</v>
+        <v>6.87</v>
       </c>
       <c r="O60" t="n">
         <v>2.01</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>9.69</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46286.38541666666</v>
+        <v>46286.55208333334</v>
       </c>
       <c r="H61" t="n">
-        <v>3560.4</v>
+        <v>3650.1</v>
       </c>
       <c r="I61" t="n">
         <v>3613.775874011003</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K61" t="n">
-        <v>5.22</v>
+        <v>2.83</v>
       </c>
       <c r="L61" t="n">
         <v>4.96</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>8.34</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>3522.4</v>
+        <v>3374.9</v>
       </c>
       <c r="I62" t="n">
         <v>3393.144737732948</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>9</v>
+        <v>9.833333333333334</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.5</v>
+        <v>-7.54</v>
       </c>
       <c r="L62" t="n">
-        <v>6.43</v>
+        <v>7.93</v>
       </c>
       <c r="M62" t="n">
         <v>1.4</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4035,6 +4790,12 @@
       <c r="Q63" t="n">
         <v>34</v>
       </c>
+      <c r="R63" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5797,7 +6558,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21.9</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -5807,7 +6568,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="7">
@@ -5817,7 +6578,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>113.2</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -5827,7 +6588,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="9">
@@ -5837,7 +6598,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26.2</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10">
@@ -5847,7 +6608,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56.2</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -5857,7 +6618,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12">
@@ -5867,7 +6628,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -5877,7 +6638,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80.3</v>
+        <v>78.7</v>
       </c>
     </row>
     <row r="14">
@@ -5887,7 +6648,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.31</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="15">
@@ -5897,7 +6658,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.65</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="16">
@@ -5907,7 +6668,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.13</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="17">
@@ -5917,7 +6678,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.56</v>
+        <v>71.77</v>
       </c>
     </row>
     <row r="18">
@@ -5927,7 +6688,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>31.1</v>
       </c>
     </row>
     <row r="19">
@@ -5937,7 +6698,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.38</v>
+        <v>8.619999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -5947,7 +6708,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.12</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="21">
@@ -5957,7 +6718,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>25.41</v>
+        <v>28.36</v>
       </c>
     </row>
     <row r="22">
@@ -5967,7 +6728,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
     </row>
     <row r="23">
@@ -5977,7 +6738,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
@@ -5987,7 +6748,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.62</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="25">
@@ -5997,7 +6758,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.16</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="26">
@@ -6007,7 +6768,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.19</v>
+        <v>5.64</v>
       </c>
     </row>
     <row r="27">
@@ -6017,7 +6778,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.23</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="28">
@@ -6027,7 +6788,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29">
